--- a/review/review_ES_20261012.xlsx
+++ b/review/review_ES_20261012.xlsx
@@ -11,7 +11,7 @@
     <sheet name="review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'review'!$A$1:$N$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'review'!$A$1:$P$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -598,10 +598,12 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,20 +659,30 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>コアカリ</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>出題基準</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>Claude Codeによる修正</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>修正案</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>コメント</t>
         </is>
@@ -730,12 +742,22 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-①（胃食道逆流症&lt;GERD&gt;、非びらん性胃食道逆流症&lt;NERD&gt;、a）</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -791,12 +813,22 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-①（胃食道逆流症&lt;GERD&gt;、非びらん性胃食道逆流症&lt;NERD&gt;、a）</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -851,15 +883,25 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：用量をGL本文で確認。変更項目：provenance.corroboration, uncertainty。根拠：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）
 [2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：根拠のない欧米との比較（要確認）を、同じGLで確認できる軽症REとの対比に差し替え。変更項目：assertion.differential。根拠：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -915,12 +957,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -976,12 +1028,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：PubMed で書誌を特定し識別子を設定。変更項目：provenance.doi, provenance.pmid, provenance.pmcid, uncertainty。根拠：PubMed・Crossref の書誌</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1037,12 +1099,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1098,13 +1170,23 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：GL本文に同じ推定値の記載があることを確認したため、主張文の括弧書き「（引用元の原典と数値は要確認）」を削除。変更項目：assertion.plain_statement_ja, uncertainty。根拠：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1160,13 +1242,23 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-025 (id: JlAKpkw)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-①（胃食道逆流症&lt;GERD&gt;、非びらん性胃食道逆流症&lt;NERD&gt;、a）</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：出典未取得だったカードに JSGE GERD GL 2021 を出典として設定。変更項目：provenance.source, provenance.doi, provenance.pmid, provenance.pmcid, provenance.url, provenance.source_license, provenance.source_class, provenance.corroboration, uncertainty。根拠：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1222,12 +1314,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-①（胃食道逆流症&lt;GERD&gt;、非びらん性胃食道逆流症&lt;NERD&gt;、a）</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R12（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-009 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1283,13 +1385,23 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-①（胃食道逆流症&lt;GERD&gt;、非びらん性胃食道逆流症&lt;NERD&gt;、a）</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：GL本文に「陰性でも否定できない」旨の記載は確認できず、代わりに感度・特異度の数値を確認したため主張文を差し替え。P-CABテストの位置づけ（FRQ）も確認。変更項目：assertion.plain_statement_ja, assertion.differential, uncertainty。根拠：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1345,13 +1457,23 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-①（胃食道逆流症&lt;GERD&gt;、非びらん性胃食道逆流症&lt;NERD&gt;、a）</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：GL本文に ARMS と「長期の薬物依存を避けたい症例」の記載がないため、GLで確認できた手術適応の記述に差し替え。変更項目：assertion.plain_statement_ja, assertion.differential, provenance.corroboration, uncertainty。根拠：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：JSGE GERD GL 2021 英語版本文（PMC8938399、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1405,10 +1527,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1464,12 +1596,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：ACG Barrett GL 2022 本文（PMC10259184）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1525,13 +1667,23 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：2022年版の本文で確認できた数値に訂正。HGDの年約7%は2022年版本文に記載がないため削除。変更項目：assertion.plain_statement_ja, provenance.corroboration, uncertainty。根拠：ACG Barrett GL 2022 本文（PMC10259184）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：ACG Barrett GL 2022 本文（PMC10259184）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1587,12 +1739,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1648,12 +1810,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：ACG Barrett GL 2022 本文（PMC10259184）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1709,13 +1881,23 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-②（逆流性食道炎（備考：Barrett上皮、Barrett食道）、a）</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：「日本では狙撃生検が中心（要確認）」は出典がないため、GL本文で確認できる対比に差し替え。変更項目：assertion.differential。根拠：ACG Barrett GL 2022 本文（PMC10259184）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：ACG Barrett GL 2022 本文（PMC10259184）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1771,12 +1953,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：AGREE 2018（PMID 30009819）の抄録。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1832,13 +2024,23 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：PubMed で書誌を特定し識別子を設定。変更項目：provenance.source, provenance.doi, provenance.pmid, provenance.pmcid, uncertainty。根拠：AGREE 2018（PMID 30009819）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：AGREE 2018（PMID 30009819）の抄録。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1892,10 +2094,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1951,13 +2163,23 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：出典未取得だったカードに Hirano 2013 を設定。所見の列挙を出典に合わせて整理（主要4所見と追加所見の狭窄）。変更項目：provenance.source, provenance.doi, provenance.pmid, provenance.source_license, provenance.source_class, assertion.plain_statement_ja, uncertainty。根拠：Hirano 2013（PMID 22619364）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Hirano 2013（PMID 22619364）の抄録。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2011,10 +2233,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2070,13 +2302,23 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R07（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-023 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Dellon ES, NEJM 2022（PMID 36546624）の抄録：Part A 組織学的寛解 60%（25/42）対 5%（2/39）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
       <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2124,12 +2366,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R08（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-024 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2183,10 +2435,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2240,10 +2502,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2299,13 +2571,23 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-03 (id: JkxnuRQ)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：「正常値データベースを75人から469人に拡大」は本文に記載がなく出典を確認できないため削除。補助検査の記述は本文で確認。変更項目：assertion.plain_statement_ja, assertion.differential, uncertainty。根拠：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2361,13 +2643,23 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：DLの閾値を本文で確認。変更項目：uncertainty。根拠：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2423,13 +2715,23 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-03 (id: JkxnuRQ)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R13（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-029 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
       <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2485,12 +2787,22 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2545,15 +2857,25 @@
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-03 (id: JkxnuRQ)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R14（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-031 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：v2 の主張文のうち、機序（IRP上昇・DL短縮）は本文に記載がないため、本文で確認できた内容に差し替え。変更項目：assertion.plain_statement_ja, uncertainty。根拠：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Chicago Classification v4.0 本文（PMC8034247、NIH著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
       <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2609,13 +2931,23 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R06（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-032 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Werner YB, NEJM 2019（PMID 31800987）の抄録：221例、83.0%対81.7%、逆流性食道炎 57/20%・44/29%、重篤AE 2.7%対7.3%。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2671,12 +3003,22 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Werner YB, NEJM 2019（PMID 31800987）の抄録：221例、83.0%対81.7%、逆流性食道炎 57/20%・44/29%、重篤AE 2.7%対7.3%。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2732,13 +3074,23 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-04 (id: JkxnuRU)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-A-①（食道アカラシア、b）</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：出典未取得で主張文に「要確認」が残っていたカード。ACG 2020 本文で推奨を確認し、出典を設定して主張文を確定。変更項目：provenance.source, provenance.doi, provenance.pmid, provenance.pmcid, provenance.url, provenance.source_license, provenance.source_class, assertion.plain_statement_ja, uncertainty。根拠：ACG アカラシアGL 2020 本文（PMC9896940）の Recommendation 9
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：ACG アカラシアGL 2020 本文（PMC9896940）の Recommendation 9。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2786,12 +3138,22 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R16（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-035 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2847,12 +3209,22 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2908,12 +3280,22 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2969,12 +3351,22 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3030,13 +3422,23 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：アセトアルデヒドの Group 1 指定（2009年10月）と遺伝要因の記載をGL本文で確認。数値は ES-092 が担う。変更項目：assertion.differential, uncertainty。根拠：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3092,13 +3494,23 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：GL本文で確認できたのは多重癌が多いことまで。頭頸部癌・胃癌の具体名と「要確認」の括弧書きを主張文から外した。変更項目：assertion.plain_statement_ja, assertion.differential, uncertainty。根拠：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3152,10 +3564,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3209,10 +3631,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3266,10 +3698,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3323,10 +3765,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3382,12 +3834,22 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3441,10 +3903,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3500,13 +3972,23 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R01（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-049 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Kato K, Lancet 2024（PMID 38876133）の抄録：601例、3年OS 72.1%対62.6%、HR 0.68、CF-RTは有意差なし。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3560,10 +4042,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="3" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3619,13 +4111,23 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R02（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-051 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Kelly RJ, NEJM 2021（PMID 33789008）の抄録：794例（532対262）、DFS 22.4対11.0か月、HR 0.69。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="3" t="inlineStr"/>
       <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3680,15 +4182,25 @@
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R03（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-052 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：一次資料（抄録）で主張文を照合したため uncertainty を更新。変更項目：uncertainty。根拠：Doki Y, NEJM 2022（PMID 35108470）の抄録：970例、PD-L1≥1%と全体集団でOS延長
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Doki Y, NEJM 2022（PMID 35108470）の抄録：970例、PD-L1≥1%と全体集団でOS延長。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3744,12 +4256,22 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Sun JM, Lancet 2021（PMID 34454674）の抄録。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr"/>
-      <c r="M52" s="3" t="inlineStr"/>
       <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3804,15 +4326,25 @@
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R04（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-054 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：5年生存率を v2 の 10.9%対3.1% から、一次資料の 10.6%対3.0% に訂正。pmid は原著のものだったため、DOI と同じ5年追跡論文の PMID に置き換え（原著の PMID は source に記載）。変更項目：assertion.plain_statement_ja, provenance.source, provenance.pmid, uncertainty。根拠：Metges JP, ESMO Open 2025（PMID 41259897）の抄録：5年生存率 10.6% 対 3.0%；Sun JM, Lancet 2021（PMID 34454674）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Metges JP, ESMO Open 2025（PMID 41259897）の抄録：5年生存率 10.6% 対 3.0%。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="3" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3868,12 +4400,22 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3929,12 +4471,22 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：日本食道学会 食道癌診療GL 2022 Part 1 本文（PMC10024303、CC BY）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3990,12 +4542,22 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-6-D-①（門脈圧亢進症、a）</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Baveno VII 本文（PMC11090185、著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4051,13 +4613,23 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-6-D-①（門脈圧亢進症、a）</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：Baveno VII 本文で推奨を確認。日本の扱いはこのカードの対象外のため「要確認」を削除。変更項目：uncertainty, provenance.corroboration。根拠：Baveno VII 本文（PMC11090185、著者稿）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Baveno VII 本文（PMC11090185、著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4111,10 +4683,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="3" t="inlineStr"/>
-      <c r="M58" s="3" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-6-D-①（門脈圧亢進症、a）</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="3" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4168,10 +4750,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="3" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-D-①（食道静脈瘤（備考：胃静脈瘤、BRTO）、a）</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4219,12 +4811,22 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-D-①（食道静脈瘤（備考：胃静脈瘤、BRTO）、a）</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R17（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-061 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr"/>
-      <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="3" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4280,13 +4882,23 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-019 (id: JlAKpkg)</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-D-①（食道静脈瘤（備考：胃静脈瘤、BRTO）、a）</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：「日本の保険適用は要確認」はこのカードの対象外のため、鑑別の記載に差し替え。変更項目：assertion.differential。根拠：Baveno VII 本文（PMC11090185、著者稿）
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Baveno VII 本文（PMC11090185、著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4342,13 +4954,23 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-019 (id: JlAKpkg)</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>医学総論 Ⅸ-3-B-①（輸血の適応と一般的注意、-）；医学総論 Ⅵ-5-F-①（吐血、-）</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R10（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-063 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Villanueva C, NEJM 2013（PMID 23281973）の抄録：921例、Hb 7 対 9 g/dL。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L62" s="3" t="inlineStr"/>
-      <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4404,12 +5026,22 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-034 (id: JlAKplU)</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-D-①（食道静脈瘤（備考：胃静脈瘤、BRTO）、a）</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Baveno VII 本文（PMC11090185、著者稿）。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4465,13 +5097,23 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-019 (id: JlAKpkg)</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-D-①（食道静脈瘤（備考：胃静脈瘤、BRTO）、a）</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R11（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-065 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：García-Pagán JC, NEJM 2010（PMID 20573925）の抄録：63例、1年生存 86%対61%。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L64" s="3" t="inlineStr"/>
-      <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr"/>
+      <c r="P64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4527,12 +5169,22 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-D-①（食道静脈瘤（備考：胃静脈瘤、BRTO）、a）</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 統合：本文を v2 の ES-R18（raw/01b_esophagus_v2.md）で全文置換。ID は v1 の ES-066 を引き継ぐ。置換前の v1 本文は git 履歴の data/facts/_staging_ES_v1.yaml にある（proposals/es_merge_map.csv、claude-code（人間が2026-10-12にチャットで委任））</t>
         </is>
       </c>
-      <c r="L65" s="3" t="inlineStr"/>
-      <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr"/>
+      <c r="P65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4586,10 +5238,20 @@
           <t>小児はESPGHANなど別のGLの対象</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="3" t="inlineStr"/>
-      <c r="M66" s="3" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr"/>
+      <c r="P66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4643,10 +5305,20 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="3" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4700,10 +5372,20 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="3" t="inlineStr"/>
-      <c r="M68" s="3" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="3" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4757,10 +5439,20 @@
           <t>75%超の数値は同GL本文の記載で、原著は未確認</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="3" t="inlineStr"/>
-      <c r="M69" s="3" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>医学総論 Ⅵ-5-B（嚥下障害（嚥下痛・通過障害・誤嚥）、-）</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4816,13 +5508,23 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：Crossref の候補（著者・誌名・年・巻が一致）から DOI を設定。変更項目：provenance.doi。根拠：PubMed・Crossref の書誌
 [2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：識別子の確定を反映し、未照合の範囲を明記。変更項目：uncertainty。根拠：PubMed・Crossref の書誌</t>
         </is>
       </c>
-      <c r="L70" s="3" t="inlineStr"/>
-      <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4878,12 +5580,22 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Cheng HT, BMC Gastroenterol 2008（PMC2533005）の本文：Zargar の6段階分類。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L71" s="3" t="inlineStr"/>
-      <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="3" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr"/>
+      <c r="P71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4939,13 +5651,23 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：Crossref の候補（著者・誌名・年・巻が一致）から DOI を設定。変更項目：provenance.doi。根拠：PubMed・Crossref の書誌
 [2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：識別子の確定を反映し、未照合の範囲を明記。変更項目：uncertainty。根拠：PubMed・Crossref の書誌</t>
         </is>
       </c>
-      <c r="L72" s="3" t="inlineStr"/>
-      <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="3" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr"/>
+      <c r="P72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5001,13 +5723,23 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-004 (id: JlAKpjc)</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-9-A-①（食道裂孔ヘルニア、a）</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 起票：欠番補完（人間が2026-10-12にチャットで委任）。出典を再調査し、自作文で作成。根拠：Kahrilas 2008（PMID 18656819）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：起票時に照合した一次資料。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L73" s="3" t="inlineStr"/>
-      <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="3" t="inlineStr"/>
+      <c r="O73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5063,12 +5795,22 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-025 (id: JlAKpkw)</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>医学総論 Ⅵ-5-B（嚥下障害（嚥下痛・通過障害・誤嚥）、-）</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 起票：欠番補完（人間が2026-10-12にチャットで委任）。出典を再調査し、自作文で作成。根拠：Abdi 2022（PMC9589134）の本文</t>
         </is>
       </c>
-      <c r="L74" s="3" t="inlineStr"/>
-      <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="3" t="inlineStr"/>
+      <c r="O74" s="3" t="inlineStr"/>
+      <c r="P74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5124,13 +5866,23 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 起票：欠番補完（人間が2026-10-12にチャットで委任）。出典を再調査し、自作文で作成。根拠：Chen 2022（PMID 36338217）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：起票時に照合した一次資料。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L75" s="3" t="inlineStr"/>
-      <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="3" t="inlineStr"/>
+      <c r="O75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5184,10 +5936,20 @@
           <t>なし（2資料で一致）</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="3" t="inlineStr"/>
-      <c r="M76" s="3" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-03-03 (id: JkxnuUo)</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅻ-1-A-⑩（単純ヘルペスウイルス感染症、a）；医学各論 Ⅻ-1-A-⑭（サイトメガロウイルス感染症、a）</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="3" t="inlineStr"/>
+      <c r="O76" s="3" t="inlineStr"/>
+      <c r="P76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5243,12 +6005,22 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅻ-1-A-⑩（単純ヘルペスウイルス感染症、a）；医学各論 Ⅻ-1-A-⑭（サイトメガロウイルス感染症、a）</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Medicine 2019（PMC6571398）の本文：HSV と CMV の潰瘍形態、治療薬。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L77" s="3" t="inlineStr"/>
-      <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="3" t="inlineStr"/>
+      <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5304,12 +6076,22 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅻ-1-A-⑩（単純ヘルペスウイルス感染症、a）；医学各論 Ⅻ-1-A-⑭（サイトメガロウイルス感染症、a）</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Medicine 2019（PMC6571398）の本文：HSV と CMV の潰瘍形態、治療薬。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L78" s="3" t="inlineStr"/>
-      <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="3" t="inlineStr"/>
+      <c r="O78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5365,13 +6147,23 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅶ-1-A-①（鉄欠乏性貧血、a）；医学総論 Ⅵ-5-B（嚥下障害（嚥下痛・通過障害・誤嚥）、-）</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 起票：欠番補完（人間が2026-10-12にチャットで委任）。出典を再調査し、自作文で作成。根拠：Novacek 2006（PMID 16978405）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：起票時に照合した一次資料。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L79" s="3" t="inlineStr"/>
-      <c r="M79" s="3" t="inlineStr"/>
       <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5427,13 +6219,23 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>医学総論 Ⅵ-5-B（嚥下障害（嚥下痛・通過障害・誤嚥）、-）</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 起票：欠番補完（人間が2026-10-12にチャットで委任）。出典を再調査し、自作文で作成。根拠：Dell'Anna 2024（PMC11475965、CC BY）の本文
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：起票時に照合した一次資料。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L80" s="3" t="inlineStr"/>
-      <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5489,13 +6291,23 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-E-①（Mallory-Weiss症候群、a）</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 起票：欠番補完（人間が2026-10-12にチャットで委任）。出典を再調査し、自作文で作成。根拠：Mertens 2024（PMID 37668412）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：起票時に照合した一次資料。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L81" s="3" t="inlineStr"/>
-      <c r="M81" s="3" t="inlineStr"/>
       <c r="N81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5549,10 +6361,20 @@
           <t>感度は総説が引用した値で、原著は未確認</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr"/>
-      <c r="M82" s="3" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-E-②（食道穿孔・破裂（備考：Boerhaave症候群）、b）</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="3" t="inlineStr"/>
+      <c r="O82" s="3" t="inlineStr"/>
+      <c r="P82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5608,12 +6430,22 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-E-②（食道穿孔・破裂（備考：Boerhaave症候群）、b）</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：Boerhaave Syndrome—Narrative Review, Diagnostics 2025（PMC12524210、CC BY）の本文：水溶性造影剤で22〜50%の穿孔を見逃す。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L83" s="3" t="inlineStr"/>
-      <c r="M83" s="3" t="inlineStr"/>
       <c r="N83" s="3" t="inlineStr"/>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5667,10 +6499,20 @@
           <t>治療の選択基準と死亡率の数値は未確認</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="3" t="inlineStr"/>
-      <c r="M84" s="3" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-E-②（食道穿孔・破裂（備考：Boerhaave症候群）、b）</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="3" t="inlineStr"/>
+      <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5726,13 +6568,23 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 起票：欠番補完（人間が2026-10-12にチャットで委任）。出典を再調査し、自作文で作成。根拠：Hirano 2013（PMID 22619364）の抄録
 [2026-10-12] status draft → verified_sources（識別子・ライセンスを API で照合済み、主張文の数値・推奨を一次資料と照合：起票時に照合した一次資料。人間が2026-10-12にチャットで委任）</t>
         </is>
       </c>
-      <c r="L85" s="3" t="inlineStr"/>
-      <c r="M85" s="3" t="inlineStr"/>
       <c r="N85" s="3" t="inlineStr"/>
+      <c r="O85" s="3" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5786,10 +6638,20 @@
           <t>該当箇所の照合が未了</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="3" t="inlineStr"/>
-      <c r="M86" s="3" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-030 (id: JlAKplE)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="3" t="inlineStr"/>
+      <c r="O86" s="3" t="inlineStr"/>
+      <c r="P86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5835,10 +6697,20 @@
           <t>PMDA添付文書の改訂履歴での確認は未実施</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr"/>
-      <c r="M87" s="3" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="3" t="inlineStr"/>
+      <c r="O87" s="3" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5886,12 +6758,22 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-5-A-②（消化管アレルギー、好酸球性胃腸炎、好酸球性食道炎、b）</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：2026年時点の国内承認状況を再調査。変更項目：uncertainty。根拠：サノフィ デュピクセント IF（2026年3月改訂 第20版）と国内報道の検索（2026-10-12）。国内のEoE承認の記録なし</t>
         </is>
       </c>
-      <c r="L88" s="3" t="inlineStr"/>
-      <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="inlineStr"/>
+      <c r="O88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5945,10 +6827,20 @@
           <t>53%は試算値（仮定に基づく推計）</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>PS-03-04-14 (id: JkxnuYE)</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-C-①（食道癌、a）</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5996,17 +6888,27 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
+          <t>PS-02-08-05 (id: JkxnuRY)；TBL-02-07-033 (id: JlAKplQ)</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>医学各論 Ⅵ-1-B-①（胃食道逆流症&lt;GERD&gt;、非びらん性胃食道逆流症&lt;NERD&gt;、a）</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
           <t>[2026-10-12] 内容照合による修正（人間が2026-10-12にチャットで委任）：令和8年度改定後も点数が変わらないことを確認。変更項目：uncertainty。根拠：診療報酬点数表（令和8年版）K653-6 12,000点（clinicalsup.jp の点数表ページ、2026-10-12 閲覧）</t>
         </is>
       </c>
-      <c r="L90" s="3" t="inlineStr"/>
-      <c r="M90" s="3" t="inlineStr"/>
       <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N90"/>
+  <autoFilter ref="A1:P90"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,修正,削除"</formula1>
     </dataValidation>
   </dataValidations>
